--- a/RothCpy-AFM_v1_template_INPUT.xlsx
+++ b/RothCpy-AFM_v1_template_INPUT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://creagov-my.sharepoint.com/personal/francesco_palazzi_crea_gov_it/Documents/Prog_MRV4SOC/Cmodels_RothC_Python/Operation_AgroForRothC_py/RothC-AF_PY_script+input_templates/RothCpy_materiale_x_ZENODO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{89128747-0954-4583-8383-52ACF81EC0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E78228A3-2969-4568-9294-834C3C902CA3}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="8_{89128747-0954-4583-8383-52ACF81EC0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{520E1013-24F9-4B05-8E39-66A7F97C12D4}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-3190" windowWidth="29020" windowHeight="15700" tabRatio="537" xr2:uid="{00AECC67-D295-4624-A5A5-1961D1DFA1DD}"/>
+    <workbookView xWindow="32220" yWindow="-11810" windowWidth="21600" windowHeight="11320" tabRatio="537" xr2:uid="{00AECC67-D295-4624-A5A5-1961D1DFA1DD}"/>
   </bookViews>
   <sheets>
     <sheet name="template_sheet" sheetId="4" r:id="rId1"/>
@@ -137,12 +137,6 @@
     <t>CROP</t>
   </si>
   <si>
-    <t>herb_share</t>
-  </si>
-  <si>
-    <t>tree_share</t>
-  </si>
-  <si>
     <t xml:space="preserve">ratio of C-inputs during spin-up - Herbaceous </t>
   </si>
   <si>
@@ -168,13 +162,19 @@
   </si>
   <si>
     <t>compile from here with the actual data for your simulation</t>
+  </si>
+  <si>
+    <t>herb_fraction</t>
+  </si>
+  <si>
+    <t>tree_fraction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,6 +204,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -286,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
@@ -396,6 +403,9 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -802,22 +812,22 @@
         <v>2</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M3" s="18"/>
       <c r="N3" s="19"/>
@@ -854,10 +864,10 @@
         <v>16</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="1"/>
@@ -922,11 +932,11 @@
         <v>18</v>
       </c>
       <c r="K6" s="43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L6" s="43"/>
       <c r="M6" s="43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N6" s="43"/>
     </row>
@@ -965,13 +975,13 @@
         <v>31</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1010,7 +1020,7 @@
       <c r="M8" s="17"/>
       <c r="N8" s="1"/>
       <c r="O8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1408,8 +1418,8 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="41" t="s">
-        <v>42</v>
+      <c r="A20" s="44" t="s">
+        <v>40</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="36"/>
@@ -2754,7 +2764,7 @@
       <c r="N103" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="miFsd+Zp+qoUf/JYC7VOMyyr1J2mHF0/0M6oFwayoOxzY6Qo8q642tXzDAYcysO3nb/uUapUmx6ItmeEPu4T4g==" saltValue="Kgy2aDY90jmg0QwnKyrCHQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xPXl4tuNueixrlK9bZTiRXHC66CuTaW/2WD1CSnEBHrlgqnVOo90Uj+1BKxhHjRTxweAyWSL9iNO+4EOum2zww==" saltValue="wx+3lMYsPLt428k0UbknxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="2">
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="M6:N6"/>
